--- a/artfynd/A 2950-2025 artfynd.xlsx
+++ b/artfynd/A 2950-2025 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>122277607</v>
       </c>
       <c r="B7" t="n">
-        <v>91184</v>
+        <v>91194</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 2950-2025 artfynd.xlsx
+++ b/artfynd/A 2950-2025 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>122277607</v>
       </c>
       <c r="B7" t="n">
-        <v>91194</v>
+        <v>91206</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 2950-2025 artfynd.xlsx
+++ b/artfynd/A 2950-2025 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>122277607</v>
       </c>
       <c r="B7" t="n">
-        <v>91206</v>
+        <v>91211</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 2950-2025 artfynd.xlsx
+++ b/artfynd/A 2950-2025 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>122277607</v>
       </c>
       <c r="B7" t="n">
-        <v>91211</v>
+        <v>91216</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1317,11 +1317,6 @@
       </c>
       <c r="E7" t="n">
         <v>5420</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Grovticka</t>
-        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>

--- a/artfynd/A 2950-2025 artfynd.xlsx
+++ b/artfynd/A 2950-2025 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>122277607</v>
       </c>
       <c r="B7" t="n">
-        <v>91216</v>
+        <v>91229</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1317,6 +1317,11 @@
       </c>
       <c r="E7" t="n">
         <v>5420</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>

--- a/artfynd/A 2950-2025 artfynd.xlsx
+++ b/artfynd/A 2950-2025 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>122277607</v>
       </c>
       <c r="B7" t="n">
-        <v>91229</v>
+        <v>91242</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 2950-2025 artfynd.xlsx
+++ b/artfynd/A 2950-2025 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>122277607</v>
       </c>
       <c r="B7" t="n">
-        <v>91242</v>
+        <v>91243</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 2950-2025 artfynd.xlsx
+++ b/artfynd/A 2950-2025 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>122277607</v>
       </c>
       <c r="B7" t="n">
-        <v>91243</v>
+        <v>91244</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
